--- a/ARM Functions/Move Edits/Ice Spinner.xlsx
+++ b/ARM Functions/Move Edits/Ice Spinner.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521F502F-00E3-4112-837B-4DC48AD183B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9E351E-CC58-4950-8C5F-4D0AA3C28B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>Address</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Ice Spinner Call Function</t>
   </si>
   <si>
-    <t>mov r1, 0x2</t>
-  </si>
-  <si>
     <t>Rapid Spin 0x63</t>
   </si>
   <si>
@@ -81,6 +78,126 @@
   </si>
   <si>
     <t>Splintered Stormshards remove terrain 0x9F</t>
+  </si>
+  <si>
+    <t>mov r1, 0x3</t>
+  </si>
+  <si>
+    <t>bl 0x00087B58</t>
+  </si>
+  <si>
+    <t>b 0x00082D44</t>
+  </si>
+  <si>
+    <t>+1 priority when terrain is active 0x11</t>
+  </si>
+  <si>
+    <t>push {r4, r5, lr}</t>
+  </si>
+  <si>
+    <t>Check self attacker</t>
+  </si>
+  <si>
+    <t>mov r5, r1</t>
+  </si>
+  <si>
+    <t>mov r4, r2</t>
+  </si>
+  <si>
+    <t>cmp r0, r4</t>
+  </si>
+  <si>
+    <t>mov r0, 0x1C</t>
+  </si>
+  <si>
+    <t>add r1, r0, 0x1</t>
+  </si>
+  <si>
+    <t>Get current priority</t>
+  </si>
+  <si>
+    <t>add 1</t>
+  </si>
+  <si>
+    <t>mov r0, r5</t>
+  </si>
+  <si>
+    <t>bl 0x000E2274</t>
+  </si>
+  <si>
+    <t>Get Terrain</t>
+  </si>
+  <si>
+    <t>cmp r0, 0x0</t>
+  </si>
+  <si>
+    <t>check terrain</t>
+  </si>
+  <si>
+    <t>do nothing if none set</t>
+  </si>
+  <si>
+    <t>000C69B4</t>
+  </si>
+  <si>
+    <t>mov r0, 0x3</t>
+  </si>
+  <si>
+    <t>30402DE9</t>
+  </si>
+  <si>
+    <t>0150A0E1</t>
+  </si>
+  <si>
+    <t>0240A0E1</t>
+  </si>
+  <si>
+    <t>0300A0E3</t>
+  </si>
+  <si>
+    <t>6304FFEB</t>
+  </si>
+  <si>
+    <t>040050E1</t>
+  </si>
+  <si>
+    <t>0900001A</t>
+  </si>
+  <si>
+    <t>0500A0E1</t>
+  </si>
+  <si>
+    <t>266E00EB</t>
+  </si>
+  <si>
+    <t>000050E3</t>
+  </si>
+  <si>
+    <t>0500000A</t>
+  </si>
+  <si>
+    <t>1C00A0E3</t>
+  </si>
+  <si>
+    <t>5B04FFEB</t>
+  </si>
+  <si>
+    <t>011080E2</t>
+  </si>
+  <si>
+    <t>3040BDE8</t>
+  </si>
+  <si>
+    <t>D2F0FEEA</t>
+  </si>
+  <si>
+    <t>3080BDE8</t>
+  </si>
+  <si>
+    <t>000C9A20</t>
+  </si>
+  <si>
+    <t>000C96F0</t>
   </si>
 </sst>
 </file>
@@ -90,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,13 +235,42 @@
       <name val="Cascadia Code"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -149,6 +295,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -484,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="3" customWidth="1"/>
@@ -518,14 +682,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
-        <v>0210A0E3</v>
+        <v>0310A0E3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -578,12 +742,272 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.45" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="str">
+        <f t="shared" ref="A17:A33" si="1">DEC2HEX(HEX2DEC(A16)+4,8)</f>
+        <v>000C69B8</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69BC</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69C0</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69C4</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69C8</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69CC</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="11" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A$33)</f>
+        <v>bne 0x000C69F8</v>
+      </c>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69D0</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69D4</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="16"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69D8</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69DC</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="15" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A33)</f>
+        <v>beq 0x000C69F8</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69E0</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69E4</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="18"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69E8</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69EC</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69F0</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <f>SUBSTITUTE(C16,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69F4</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="21"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>000C69F8</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>SUBSTITUTE(C31,"lr","pc")</f>
+        <v>pop {r4, r5, pc}</v>
       </c>
     </row>
   </sheetData>
